--- a/src/analysis/participant_word_mis-aligned.xlsx
+++ b/src/analysis/participant_word_mis-aligned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="B1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,110 +440,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>maebog</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>muun</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>paemul</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>pipog</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>pogab</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>siljog</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>songbu</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>suha</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>830</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
